--- a/public/templates/CPT_Code.xlsx
+++ b/public/templates/CPT_Code.xlsx
@@ -1,145 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAL WEB\OneDrive\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BABB8E3E-ED61-430F-8F18-70B9D752C667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="in" sheetId="1" r:id="rId1"/>
-    <sheet name="lists" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="in" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lists2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lists" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_dropdowns" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="categories">lists!$B$1:$B$11</definedName>
+    <definedName name="CategoryList">lists!$A$1:$A$9</definedName>
+    <definedName name="ServiceCategoryList">lists2!$A$1:$A$88</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>EVALUATION_AND_MANAGEMENT</t>
-  </si>
-  <si>
-    <t>Evaluation and management</t>
-  </si>
-  <si>
-    <t>ANESTHESIA</t>
-  </si>
-  <si>
-    <t>Anesthesia</t>
-  </si>
-  <si>
-    <t>RADIOLOGY</t>
-  </si>
-  <si>
-    <t>Radiology</t>
-  </si>
-  <si>
-    <t>PATHOLOGY_AND_LABORATORY</t>
-  </si>
-  <si>
-    <t>Pathology and laboratory</t>
-  </si>
-  <si>
-    <t>SURGERY</t>
-  </si>
-  <si>
-    <t>Surgery</t>
-  </si>
-  <si>
-    <t>VISIT</t>
-  </si>
-  <si>
-    <t>Visit</t>
-  </si>
-  <si>
-    <t>UNDEFINED</t>
-  </si>
-  <si>
-    <t>Undefined</t>
-  </si>
-  <si>
-    <t>VACCINES</t>
-  </si>
-  <si>
-    <t>Vaccines</t>
-  </si>
-  <si>
-    <t>MEDICATION_ADMINISTRATION</t>
-  </si>
-  <si>
-    <t>Medication administration</t>
-  </si>
-  <si>
-    <t>EXAMINATION_AND_SERVICES</t>
-  </si>
-  <si>
-    <t>Examination and services</t>
-  </si>
-  <si>
-    <t>TEMPORARY_CODES</t>
-  </si>
-  <si>
-    <t>Temporary codes</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -158,22 +59,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -473,154 +433,1440 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col width="13.88671875" customWidth="1" min="1" max="1"/>
+    <col width="18.5546875" customWidth="1" min="2" max="2"/>
+    <col width="14.44140625" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>service_category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=ServiceCategoryList</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=CategoryList</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Code required" error="Please fill the 'code' cell first (column A)." promptTitle="Choose a category" prompt="Dropdown shows pretty labels; background stores RAW codes on the lists sheet." xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>IF($A160&lt;&gt;"",lists!$B$1:$B$11,"")</xm:f>
-          </x14:formula1>
-          <xm:sqref>C160:C5000</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Code required" error="Please fill the 'code' cell first (column A)." promptTitle="Choose a category" prompt="Excel Online version: dropdown pulls from lists!B1:B1000 when code is present." xr:uid="{00000000-0002-0000-0000-000087130000}">
-          <x14:formula1>
-            <xm:f>IF($A160&lt;&gt;"",lists!$B$1:$B$1000,"")</xm:f>
-          </x14:formula1>
-          <xm:sqref>C160:C5000</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4F779ADB-1D8F-4D60-9C52-7CE68BD9970D}">
-          <x14:formula1>
-            <xm:f>IF($A2&lt;&gt;"",lists!$B$1:$B$1000,"")</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C159</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Amniocentesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Anaesthesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anaesthesia Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Analgesic Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Anatomic Patholgy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bariatric Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Blood Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Blood Bank Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bone Densomitry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cardiac Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chest Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Computed Tomography Scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Consulatation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Dental Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Dermatology</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dermatology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ent</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ent Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gastroenterology</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gastroenterology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>General Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>General Surgery Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Genetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gynaecology And Obstetrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gynaecology And Obstetrics Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Haematology</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Immunization</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Immunology</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Internal Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Internal Medicine Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ivf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Laboratory Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Laparoscopy</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Maxillofacial Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Microbiology</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Mri</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Mri With Contrast</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mri Without Contrast</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Neonatology</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Nephrology</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Nephrology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Neurology</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Neurology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Neurosurgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Nuclear Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Nuclear Medicine Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Oncology</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ophthalmology</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ophthalmology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Oral And Maxillofacial Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Orthopedic</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Orthopedic Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Otorhinolaryngology</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Paediatrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Paediatrics Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Physiotherapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Plastic Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Plastic Surgery Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Psychiatry</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Radiology</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Radiology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Rehabilitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Renal Dialysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Surgical Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ultrasound Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Urology</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Urology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Vaccination</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Vascular Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Vascular Surgery Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>X Ray</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>X Ray Procedure</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="38.109375" customWidth="1"/>
-    <col min="2" max="2" width="27.5546875" customWidth="1"/>
+    <col width="38.109375" customWidth="1" min="1" max="1"/>
+    <col width="27.5546875" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Radiology</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Surgical Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Physiotherapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Immunization</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Radiology</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Amniocentesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anaesthesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Surgical Procedure</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anaesthesia Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Analgesic Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Physiotherapy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Anatomic Patholgy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Immunization</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bariatric Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Blood Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Blood Bank Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bone Densomitry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cardiac Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chest Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Computed Tomography Scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Consulatation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dental Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dermatology</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dermatology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ent</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ent Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gastroenterology</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gastroenterology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>General Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>General Surgery Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Genetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gynaecology And Obstetrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gynaecology And Obstetrics Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Haematology</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Immunization</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Immunology</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Internal Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Internal Medicine Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ivf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Laboratory Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Laparoscopy</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Maxillofacial Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Microbiology</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mri</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mri With Contrast</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mri Without Contrast</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Neonatology</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nephrology</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nephrology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Neurology</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Neurology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Neurosurgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nuclear Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nuclear Medicine Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Oncology</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ophthalmology</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ophthalmology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Oral And Maxillofacial Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Orthopedic</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Orthopedic Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Otorhinolaryngology</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Paediatrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Paediatrics Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Physiotherapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Plastic Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Plastic Surgery Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Psychiatry</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Radiology</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Radiology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Rehabilitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Renal Dialysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Surgical Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ultrasound Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Urology</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Urology Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Vaccination</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Vascular Surgery</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Vascular Surgery Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>X Ray</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>X Ray Procedure</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
